--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50561093-5112-4423-93C1-3208369306A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C6F9EF-187E-4199-B55B-7823F9E9B767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="2">
-        <v>0.46717592592592594</v>
+        <v>0.78317129629629634</v>
       </c>
       <c r="I3" s="1">
         <v>46170.418749999997</v>
@@ -808,7 +808,7 @@
         <v>12</v>
       </c>
       <c r="H12" s="2">
-        <v>3.5787037037037034E-2</v>
+        <v>3.5821759259259262E-2</v>
       </c>
       <c r="I12" s="1">
         <v>46176.880439814813</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEF16382-6698-4DFD-B0E6-C45DA9970FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E1EFDDF-D986-4B40-B386-8AF1C59788E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="43">
   <si>
     <t>Company Name</t>
   </si>
@@ -89,16 +89,19 @@
     <t>Mark Complete</t>
   </si>
   <si>
+    <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
     <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
   </si>
   <si>
     <t>Express Tow and Recovery</t>
   </si>
   <si>
     <t>Cornine, Harold</t>
-  </si>
-  <si>
-    <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
   </si>
   <si>
     <t>Davis, Luke D</t>
@@ -162,6 +165,9 @@
   </si>
   <si>
     <t>Younker, Rylee</t>
+  </si>
+  <si>
+    <t>Mcfadin, Nicholas R.</t>
   </si>
 </sst>
 </file>
@@ -535,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -584,16 +590,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>5751</v>
       </c>
       <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -613,16 +619,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>5499</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>12</v>
@@ -651,16 +657,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>5493</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>14</v>
@@ -689,16 +695,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>5494</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>12</v>
@@ -727,16 +733,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>5751</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -756,16 +762,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10">
         <v>5497</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>12</v>
@@ -794,22 +800,22 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>5499</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="J12" s="2">
-        <v>3.5821759259259262E-2</v>
+        <v>3.591435185185185E-2</v>
       </c>
       <c r="K12" s="1">
         <v>46176.880439814813</v>
@@ -832,16 +838,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>5500</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>14</v>
@@ -870,16 +876,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16">
         <v>5501</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>12</v>
@@ -908,16 +914,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <v>5503</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -937,16 +943,16 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <v>5504</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -966,16 +972,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>5505</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -995,16 +1001,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21">
         <v>5506</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
@@ -1024,16 +1030,16 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E22">
         <v>5507</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1053,22 +1059,22 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E23">
         <v>5508</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J23" s="2">
-        <v>0</v>
+        <v>2.199074074074074E-4</v>
       </c>
       <c r="K23" s="1">
         <v>46176.883912037039</v>
@@ -1081,55 +1087,35 @@
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24">
-        <v>5509</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>46176.884606481479</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="1"/>
       <c r="M24" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E25">
-        <v>5654</v>
+        <v>5509</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J25" s="2">
-        <v>9.1435185185185178E-3</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>46176.885300925926</v>
+        <v>46176.884606481479</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1140,22 +1126,22 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E26">
-        <v>5510</v>
+        <v>5654</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J26" s="2">
-        <v>0</v>
+        <v>9.1435185185185178E-3</v>
       </c>
       <c r="K26" s="1">
         <v>46176.885300925926</v>
@@ -1169,25 +1155,25 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27">
-        <v>5511</v>
+        <v>5510</v>
       </c>
       <c r="F27" t="s">
         <v>35</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J27" s="2">
-        <v>6.8171296296296296E-3</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>46176.885995370372</v>
+        <v>46176.885300925926</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1198,25 +1184,25 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E28">
-        <v>5515</v>
+        <v>5511</v>
       </c>
       <c r="F28" t="s">
         <v>36</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J28" s="2">
-        <v>1.3888888888888889E-4</v>
+        <v>6.8171296296296296E-3</v>
       </c>
       <c r="K28" s="1">
-        <v>46176.886689814812</v>
+        <v>46176.885995370372</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1226,64 +1212,64 @@
       </c>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H29" s="2"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="1"/>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29">
+        <v>5515</v>
+      </c>
+      <c r="F29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="K29" s="1">
+        <v>46176.886689814812</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
       <c r="M29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="H30" s="2"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="1"/>
+      <c r="M30" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30">
-        <v>5517</v>
-      </c>
-      <c r="F30" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0.14811342592592591</v>
-      </c>
-      <c r="K30" s="1">
-        <v>46176.886689814812</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31">
-        <v>5518</v>
+        <v>5517</v>
       </c>
       <c r="F31" t="s">
         <v>38</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J31" s="2">
-        <v>0</v>
+        <v>0.14811342592592591</v>
       </c>
       <c r="K31" s="1">
-        <v>46176.887384259258</v>
+        <v>46176.886689814812</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1294,16 +1280,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E32">
-        <v>5519</v>
+        <v>5518</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1312,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>46176.888078703705</v>
+        <v>46176.887384259258</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1323,16 +1309,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E33">
-        <v>5777</v>
+        <v>5519</v>
       </c>
       <c r="F33" t="s">
         <v>40</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1351,186 +1337,747 @@
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H34" s="2"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="1"/>
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34">
+        <v>5777</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>46176.888078703705</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="1"/>
+      <c r="D35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35">
+        <v>5493</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" s="2">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="K35" s="1">
+        <v>46210.752662037034</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="2"/>
       <c r="K36" s="1"/>
+      <c r="M36" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="1"/>
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37">
+        <v>5494</v>
+      </c>
+      <c r="F37" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>46210.75335648148</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="1"/>
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38">
+        <v>5751</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" s="2">
+        <v>6.6782407407407407E-3</v>
+      </c>
+      <c r="K38" s="1">
+        <v>46210.75335648148</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="1"/>
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39">
+        <v>5497</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J39" s="2">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="K39" s="1">
+        <v>46210.754050925927</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H40" s="2"/>
       <c r="I40" s="1"/>
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
+      <c r="M40" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H41" s="2"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="1"/>
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41">
+        <v>5499</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="2">
+        <v>6.3657407407407404E-3</v>
+      </c>
+      <c r="K41" s="1">
+        <v>46210.754745370374</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H42" s="2"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="1"/>
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42">
+        <v>5500</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>46210.755439814813</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H43" s="2"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="1"/>
+      <c r="D43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43">
+        <v>5501</v>
+      </c>
+      <c r="F43" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>46210.75613425926</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H44" s="2"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="1"/>
+      <c r="D44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44">
+        <v>5503</v>
+      </c>
+      <c r="F44" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="2">
+        <v>6.5856481481481478E-3</v>
+      </c>
+      <c r="K44" s="1">
+        <v>46210.75613425926</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="1"/>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45">
+        <v>5504</v>
+      </c>
+      <c r="F45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>46210.756828703707</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H46" s="2"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="1"/>
+      <c r="D46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46">
+        <v>5505</v>
+      </c>
+      <c r="F46" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J46" s="2">
+        <v>7.0486111111111114E-3</v>
+      </c>
+      <c r="K46" s="1">
+        <v>46210.757523148146</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H47" s="2"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="1"/>
+      <c r="D47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47">
+        <v>5506</v>
+      </c>
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="2">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>46210.758217592593</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H48" s="2"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H49" s="2"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H50" s="2"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="1"/>
-    </row>
-    <row r="51" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H51" s="2"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="1"/>
-    </row>
-    <row r="52" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H52" s="2"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="1"/>
-    </row>
-    <row r="53" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H53" s="2"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="1"/>
-    </row>
-    <row r="54" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H54" s="2"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="1"/>
-    </row>
-    <row r="55" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H55" s="2"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="1"/>
-    </row>
-    <row r="56" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H56" s="2"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="1"/>
-    </row>
-    <row r="57" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48">
+        <v>5507</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J48" s="2">
+        <v>8.8425925925925929E-3</v>
+      </c>
+      <c r="K48" s="1">
+        <v>46210.758217592593</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49">
+        <v>5508</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>46210.758912037039</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50">
+        <v>5509</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="2">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>46210.759606481479</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51">
+        <v>5942</v>
+      </c>
+      <c r="F51" t="s">
+        <v>42</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="2">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>46210.760300925926</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52">
+        <v>5654</v>
+      </c>
+      <c r="F52" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="2">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>46210.760995370372</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53">
+        <v>5510</v>
+      </c>
+      <c r="F53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="2">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>46210.760995370372</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54">
+        <v>5511</v>
+      </c>
+      <c r="F54" t="s">
+        <v>36</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J54" s="2">
+        <v>5.7754629629629631E-3</v>
+      </c>
+      <c r="K54" s="1">
+        <v>46210.761689814812</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55">
+        <v>5515</v>
+      </c>
+      <c r="F55" t="s">
+        <v>37</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>46210.762384259258</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56">
+        <v>5517</v>
+      </c>
+      <c r="F56" t="s">
+        <v>38</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>46210.763078703705</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H57" s="2"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2"/>
       <c r="K57" s="1"/>
-    </row>
-    <row r="58" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H58" s="2"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="1"/>
-    </row>
-    <row r="59" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H59" s="2"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="1"/>
-    </row>
-    <row r="60" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H60" s="2"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="1"/>
-    </row>
-    <row r="61" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58">
+        <v>5518</v>
+      </c>
+      <c r="F58" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J58" s="2">
+        <v>6.1921296296296299E-3</v>
+      </c>
+      <c r="K58" s="1">
+        <v>46210.763773148145</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59">
+        <v>5519</v>
+      </c>
+      <c r="F59" t="s">
+        <v>40</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="2">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
+        <v>46210.763773148145</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60">
+        <v>5777</v>
+      </c>
+      <c r="F60" t="s">
+        <v>41</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J60" s="2">
+        <v>6.0185185185185185E-3</v>
+      </c>
+      <c r="K60" s="1">
+        <v>46210.764467592591</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H61" s="2"/>
       <c r="I61" s="1"/>
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
     </row>
-    <row r="62" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H62" s="2"/>
       <c r="I62" s="1"/>
       <c r="J62" s="2"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H63" s="2"/>
       <c r="I63" s="1"/>
       <c r="J63" s="2"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H64" s="2"/>
       <c r="I64" s="1"/>
       <c r="J64" s="2"/>
@@ -3417,6 +3964,7 @@
     <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" s="2"/>
       <c r="I378" s="1"/>
+      <c r="J378" s="2"/>
       <c r="K378" s="1"/>
     </row>
     <row r="379" spans="8:11" x14ac:dyDescent="0.3">
@@ -39484,7 +40032,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E1EFDDF-D986-4B40-B386-8AF1C59788E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7C27CF7-61B3-4051-9ADA-7337541D3397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -89,10 +89,10 @@
     <t>Mark Complete</t>
   </si>
   <si>
-    <t>Alert Driving: Big Three</t>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>Camera Event Management Orientation for Drivers</t>
+    <t>Alert Driving: Big Three</t>
   </si>
   <si>
     <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -634,7 +634,7 @@
         <v>12</v>
       </c>
       <c r="J3" s="2">
-        <v>0.78317129629629634</v>
+        <v>0.79847222222222225</v>
       </c>
       <c r="K3" s="1">
         <v>46170.418749999997</v>
@@ -666,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>14</v>
@@ -704,7 +704,7 @@
         <v>23</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>12</v>
@@ -742,7 +742,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -771,7 +771,7 @@
         <v>24</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>12</v>
@@ -809,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>12</v>
@@ -847,7 +847,7 @@
         <v>25</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>14</v>
@@ -885,7 +885,7 @@
         <v>26</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>12</v>
@@ -923,7 +923,7 @@
         <v>27</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -952,7 +952,7 @@
         <v>28</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -981,7 +981,7 @@
         <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
@@ -1039,7 +1039,7 @@
         <v>31</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>32</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>12</v>
@@ -1106,7 +1106,7 @@
         <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>13</v>
@@ -1135,7 +1135,7 @@
         <v>34</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>35</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -1193,7 +1193,7 @@
         <v>36</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>37</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>12</v>
@@ -1260,7 +1260,7 @@
         <v>38</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1289,7 +1289,7 @@
         <v>39</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1318,7 +1318,7 @@
         <v>40</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1347,7 +1347,7 @@
         <v>41</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1376,7 +1376,7 @@
         <v>22</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>12</v>
@@ -1414,7 +1414,7 @@
         <v>23</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1443,7 +1443,7 @@
         <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1472,7 +1472,7 @@
         <v>24</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>12</v>
@@ -1510,7 +1510,7 @@
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1539,7 +1539,7 @@
         <v>25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1568,7 +1568,7 @@
         <v>26</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1597,7 +1597,7 @@
         <v>27</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1626,7 +1626,7 @@
         <v>28</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -1655,7 +1655,7 @@
         <v>29</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1684,7 +1684,7 @@
         <v>30</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>13</v>
@@ -1713,7 +1713,7 @@
         <v>31</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1742,7 +1742,7 @@
         <v>32</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -1771,7 +1771,7 @@
         <v>33</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -1800,7 +1800,7 @@
         <v>42</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -1829,7 +1829,7 @@
         <v>34</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>13</v>
@@ -1858,7 +1858,7 @@
         <v>35</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -1887,7 +1887,7 @@
         <v>36</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -1916,7 +1916,7 @@
         <v>37</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>13</v>
@@ -1945,7 +1945,7 @@
         <v>38</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>14</v>
@@ -1983,7 +1983,7 @@
         <v>39</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2012,7 +2012,7 @@
         <v>40</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2041,7 +2041,7 @@
         <v>41</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -5877,6 +5877,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -6186,6 +6187,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -6275,6 +6277,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -6381,6 +6384,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -6398,6 +6402,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -6409,6 +6414,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -6450,6 +6456,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -6473,6 +6480,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -6496,6 +6504,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -6513,6 +6522,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -6524,11 +6534,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -6648,6 +6660,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -6731,6 +6744,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -6754,6 +6768,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -6765,6 +6780,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -6776,6 +6792,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -6823,6 +6840,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -6876,6 +6894,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -7048,6 +7067,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -7059,6 +7079,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -7136,6 +7157,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -7153,6 +7175,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -7200,6 +7223,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -7312,6 +7336,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -7371,6 +7396,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -7382,6 +7408,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -7453,6 +7480,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -7505,6 +7533,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -7581,11 +7610,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -7645,6 +7676,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -7656,6 +7688,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -7667,11 +7700,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -7725,6 +7760,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -7741,6 +7777,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -7764,6 +7801,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -7781,6 +7819,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -7827,11 +7866,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -7873,11 +7914,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -7895,6 +7938,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -7906,6 +7950,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -7917,6 +7962,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -7934,6 +7980,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -8011,6 +8058,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -8040,6 +8088,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -8051,16 +8100,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -8072,16 +8124,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -8093,11 +8148,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -8121,6 +8178,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -8162,6 +8220,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -8191,21 +8250,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -8217,6 +8280,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -8234,6 +8298,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -8273,11 +8338,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -8325,6 +8392,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -8354,6 +8422,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -8430,6 +8499,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -8476,6 +8546,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -8511,11 +8582,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -8532,6 +8605,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -8542,6 +8616,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -8577,6 +8652,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -8588,6 +8664,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -8599,6 +8676,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -8610,6 +8688,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -8621,6 +8700,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -8662,6 +8742,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -8679,6 +8760,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -8696,6 +8778,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -8737,6 +8820,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -8760,6 +8844,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -8806,6 +8891,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -8841,6 +8927,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -8864,6 +8951,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -8904,6 +8992,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -8921,11 +9010,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -8984,6 +9075,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -9000,6 +9092,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -9011,6 +9104,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -9022,11 +9116,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -9062,6 +9158,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -9114,6 +9211,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -9124,6 +9222,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -9139,6 +9238,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -9162,16 +9262,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -9242,6 +9345,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -9253,6 +9357,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -9353,6 +9458,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -9409,6 +9516,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -9432,6 +9540,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -9556,6 +9665,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -9714,6 +9824,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -9731,6 +9842,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -9771,6 +9883,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -10103,6 +10216,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -10191,6 +10305,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -10284,6 +10399,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -10343,11 +10459,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -10399,6 +10517,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -10440,6 +10559,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -10484,6 +10604,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -10530,11 +10651,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -10732,6 +10855,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -10761,6 +10885,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -10776,6 +10902,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -10835,6 +10962,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -10906,6 +11034,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -10947,6 +11076,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -11065,6 +11195,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -11129,6 +11260,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -11253,6 +11385,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -11479,6 +11612,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -11596,6 +11730,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -11679,6 +11814,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -11738,6 +11874,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -11761,6 +11898,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -11808,6 +11946,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -11867,6 +12006,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -11890,6 +12030,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -11907,6 +12048,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -11990,6 +12132,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -12181,6 +12324,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -40037,6 +40181,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -40044,6 +40189,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -40051,6 +40197,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -40066,6 +40213,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -40075,6 +40223,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -40082,9 +40231,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -40092,12 +40247,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -40105,12 +40263,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -40122,9 +40283,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -40139,6 +40302,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -40165,6 +40329,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -40175,7 +40340,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -40183,6 +40353,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -40194,6 +40365,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -40201,6 +40373,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -40215,13 +40388,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -40232,15 +40411,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -40256,6 +40438,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -40274,6 +40457,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -40285,6 +40469,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -40302,18 +40487,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -40342,6 +40532,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -40349,9 +40540,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -40374,12 +40567,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -40394,9 +40590,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -40412,12 +40610,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -40438,6 +40638,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -40449,9 +40650,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -40463,6 +40666,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -40502,9 +40706,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -40512,9 +40718,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -40525,6 +40733,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -40532,18 +40741,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -40551,6 +40768,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -40561,6 +40779,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -40587,15 +40806,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -40617,6 +40840,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -40624,9 +40848,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -40634,6 +40860,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -40645,6 +40872,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -40659,6 +40887,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -40668,6 +40900,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -40679,6 +40912,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -40689,10 +40923,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -40700,6 +40939,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -40714,6 +40954,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -40736,6 +40977,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -40755,25 +40997,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -40781,6 +41035,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -40788,15 +41043,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -40810,6 +41072,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -40828,9 +41091,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -40838,9 +41103,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -40848,6 +41115,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -40864,10 +41132,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB020776-CA0F-49E2-8B97-359197F688E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D167E30F-F611-47AC-AF70-63A12DD3075A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="46">
   <si>
     <t>Company Name</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Speed Mangement-C</t>
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
@@ -168,6 +171,12 @@
   </si>
   <si>
     <t>Mcfadin, Nicholas R.</t>
+  </si>
+  <si>
+    <t>Mixson, Louis</t>
+  </si>
+  <si>
+    <t>Snow, Kevin Trent</t>
   </si>
 </sst>
 </file>
@@ -541,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -556,50 +565,50 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>5751</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -617,18 +626,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>5499</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -646,7 +655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H4" s="2"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
@@ -654,18 +663,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>5493</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
@@ -683,7 +692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
       <c r="J6" s="2"/>
@@ -691,18 +700,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>5494</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -720,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
       <c r="J8" s="2"/>
@@ -728,18 +737,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>5751</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -757,18 +766,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>5497</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -786,7 +795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2"/>
@@ -794,18 +803,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>5499</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -823,7 +832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2"/>
@@ -831,18 +840,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14">
         <v>5500</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
@@ -860,7 +869,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2"/>
@@ -868,18 +877,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>5501</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -907,16 +916,16 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5503</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
@@ -936,16 +945,16 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>5504</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
         <v>10</v>
@@ -965,16 +974,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20">
         <v>5505</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -994,16 +1003,16 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21">
         <v>5506</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -1023,16 +1032,16 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22">
         <v>5507</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
@@ -1052,16 +1061,16 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23">
         <v>5508</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
         <v>12</v>
@@ -1089,16 +1098,16 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25">
         <v>5509</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
@@ -1118,16 +1127,16 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26">
         <v>5654</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1147,16 +1156,16 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27">
         <v>5510</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
@@ -1176,16 +1185,16 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C28">
         <v>5511</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
         <v>10</v>
@@ -1205,16 +1214,16 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29">
         <v>5515</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
@@ -1242,16 +1251,16 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C31">
         <v>5517</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
         <v>10</v>
@@ -1271,16 +1280,16 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C32">
         <v>5518</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1300,16 +1309,16 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33">
         <v>5519</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
@@ -1329,16 +1338,16 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C34">
         <v>5777</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -1358,13 +1367,13 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C35">
         <v>5493</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -1395,13 +1404,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C37">
         <v>5494</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -1432,13 +1441,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39">
         <v>5751</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
@@ -1461,13 +1470,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C40">
         <v>5497</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -1498,13 +1507,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C42">
         <v>5499</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -1527,13 +1536,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C43">
         <v>5500</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -1556,13 +1565,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C44">
         <v>5501</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
@@ -1585,13 +1594,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C45">
         <v>5503</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
@@ -1614,13 +1623,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C46">
         <v>5504</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -1651,13 +1660,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C48">
         <v>5505</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -1680,13 +1689,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C49">
         <v>5506</v>
       </c>
       <c r="D49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -1709,13 +1718,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C50">
         <v>5507</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -1738,13 +1747,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C51">
         <v>5508</v>
       </c>
       <c r="D51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -1767,13 +1776,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C52">
         <v>5509</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -1796,13 +1805,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C53">
         <v>5942</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -1825,13 +1834,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C54">
         <v>5654</v>
       </c>
       <c r="D54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
@@ -1854,13 +1863,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C55">
         <v>5510</v>
       </c>
       <c r="D55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
@@ -1883,13 +1892,13 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C56">
         <v>5511</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
@@ -1912,13 +1921,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C57">
         <v>5515</v>
       </c>
       <c r="D57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -1941,19 +1950,19 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C58">
         <v>5517</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H58" s="2">
         <v>8.6805555555555551E-4</v>
@@ -1969,22 +1978,43 @@
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H59" s="2"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="2"/>
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59">
+        <v>5518</v>
+      </c>
+      <c r="D59" t="s">
+        <v>40</v>
+      </c>
+      <c r="F59" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="2">
+        <v>6.1921296296296299E-3</v>
+      </c>
+      <c r="I59" s="1">
+        <v>46210.763773148145</v>
+      </c>
+      <c r="J59" s="2">
+        <v>0</v>
+      </c>
       <c r="K59" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C60">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -1993,13 +2023,13 @@
         <v>10</v>
       </c>
       <c r="H60" s="2">
-        <v>6.1921296296296299E-3</v>
+        <v>1.0833333333333334E-2</v>
       </c>
       <c r="I60" s="1">
         <v>46210.763773148145</v>
       </c>
       <c r="J60" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>11</v>
@@ -2007,13 +2037,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C61">
-        <v>5519</v>
+        <v>5777</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -2022,13 +2052,13 @@
         <v>10</v>
       </c>
       <c r="H61" s="2">
-        <v>1.0833333333333334E-2</v>
+        <v>6.0185185185185185E-3</v>
       </c>
       <c r="I61" s="1">
-        <v>46210.763773148145</v>
+        <v>46210.764467592591</v>
       </c>
       <c r="J61" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>11</v>
@@ -2036,25 +2066,25 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C62">
-        <v>5777</v>
+        <v>5493</v>
       </c>
       <c r="D62" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H62" s="2">
-        <v>6.0185185185185185E-3</v>
+        <v>8.1018518518518516E-5</v>
       </c>
       <c r="I62" s="1">
-        <v>46210.764467592591</v>
+        <v>46240.584837962961</v>
       </c>
       <c r="J62" s="2">
         <v>0</v>
@@ -2067,201 +2097,669 @@
       <c r="H63" s="2"/>
       <c r="I63" s="1"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="1"/>
+      <c r="K63" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H64" s="2"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="1"/>
-    </row>
-    <row r="65" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H65" s="2"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="1"/>
-    </row>
-    <row r="66" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H66" s="2"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="1"/>
-    </row>
-    <row r="67" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64">
+        <v>5494</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" t="s">
+        <v>17</v>
+      </c>
+      <c r="G64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="2">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>46240.584837962961</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65">
+        <v>5497</v>
+      </c>
+      <c r="D65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" s="2">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>46240.585532407407</v>
+      </c>
+      <c r="J65" s="2">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66">
+        <v>5499</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" s="2">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="I66" s="1">
+        <v>46240.586226851854</v>
+      </c>
+      <c r="J66" s="2">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H67" s="2"/>
       <c r="I67" s="1"/>
       <c r="J67" s="2"/>
-      <c r="K67" s="1"/>
-    </row>
-    <row r="68" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H68" s="2"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="1"/>
-    </row>
-    <row r="69" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H69" s="2"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="1"/>
-    </row>
-    <row r="70" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H70" s="2"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="1"/>
-    </row>
-    <row r="71" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H71" s="2"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="1"/>
-    </row>
-    <row r="72" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K67" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68">
+        <v>5500</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="F68" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="2">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>46240.586226851854</v>
+      </c>
+      <c r="J68" s="2">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69">
+        <v>5501</v>
+      </c>
+      <c r="D69" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="2">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>46240.586921296293</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70">
+        <v>5503</v>
+      </c>
+      <c r="D70" t="s">
+        <v>28</v>
+      </c>
+      <c r="F70" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" s="2">
+        <v>8.6342592592592599E-3</v>
+      </c>
+      <c r="I70" s="1">
+        <v>46240.58761574074</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71">
+        <v>5505</v>
+      </c>
+      <c r="D71" t="s">
+        <v>30</v>
+      </c>
+      <c r="F71" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="2">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="I71" s="1">
+        <v>46240.588310185187</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H72" s="2"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
-      <c r="K72" s="1"/>
-    </row>
-    <row r="73" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="2"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="1"/>
-    </row>
-    <row r="74" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H74" s="2"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="1"/>
-    </row>
-    <row r="75" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H75" s="2"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="1"/>
-    </row>
-    <row r="76" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H76" s="2"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="1"/>
-    </row>
-    <row r="77" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K72" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73">
+        <v>5507</v>
+      </c>
+      <c r="D73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" s="2">
+        <v>9.0393518518518522E-3</v>
+      </c>
+      <c r="I73" s="1">
+        <v>46240.589004629626</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74">
+        <v>5508</v>
+      </c>
+      <c r="D74" t="s">
+        <v>33</v>
+      </c>
+      <c r="F74" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>46240.589004629626</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75">
+        <v>5509</v>
+      </c>
+      <c r="D75" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="2">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <v>46240.589699074073</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76">
+        <v>5942</v>
+      </c>
+      <c r="D76" t="s">
+        <v>43</v>
+      </c>
+      <c r="F76" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" s="2">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>46240.59039351852</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H77" s="2"/>
       <c r="I77" s="1"/>
       <c r="J77" s="2"/>
-      <c r="K77" s="1"/>
-    </row>
-    <row r="78" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H78" s="2"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="1"/>
-    </row>
-    <row r="79" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H79" s="2"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="1"/>
-    </row>
-    <row r="80" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H80" s="2"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="1"/>
-    </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H81" s="2"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="1"/>
-    </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H82" s="2"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="1"/>
-    </row>
-    <row r="83" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H83" s="2"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="1"/>
-    </row>
-    <row r="84" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H84" s="2"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="1"/>
-    </row>
-    <row r="85" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H85" s="2"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="1"/>
-    </row>
-    <row r="86" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H86" s="2"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="1"/>
-    </row>
-    <row r="87" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K77" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78">
+        <v>5654</v>
+      </c>
+      <c r="D78" t="s">
+        <v>35</v>
+      </c>
+      <c r="F78" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="2">
+        <v>0</v>
+      </c>
+      <c r="I78" s="1">
+        <v>46240.59039351852</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79">
+        <v>6025</v>
+      </c>
+      <c r="D79" t="s">
+        <v>44</v>
+      </c>
+      <c r="F79" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="2">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>46240.591087962966</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80">
+        <v>5511</v>
+      </c>
+      <c r="D80" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="2">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1">
+        <v>46240.591782407406</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81">
+        <v>5515</v>
+      </c>
+      <c r="D81" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="2">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>46240.592476851853</v>
+      </c>
+      <c r="J81" s="2">
+        <v>1</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82">
+        <v>6026</v>
+      </c>
+      <c r="D82" t="s">
+        <v>45</v>
+      </c>
+      <c r="F82" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" t="s">
+        <v>10</v>
+      </c>
+      <c r="H82" s="2">
+        <v>7.3726851851851852E-3</v>
+      </c>
+      <c r="I82" s="1">
+        <v>46240.592476851853</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83">
+        <v>5517</v>
+      </c>
+      <c r="D83" t="s">
+        <v>39</v>
+      </c>
+      <c r="F83" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" s="2">
+        <v>6.9907407407407409E-3</v>
+      </c>
+      <c r="I83" s="1">
+        <v>46240.593171296299</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <v>5518</v>
+      </c>
+      <c r="D84" t="s">
+        <v>40</v>
+      </c>
+      <c r="F84" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="2">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>46240.593865740739</v>
+      </c>
+      <c r="J84" s="2">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85">
+        <v>5519</v>
+      </c>
+      <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="F85" t="s">
+        <v>17</v>
+      </c>
+      <c r="G85" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" s="2">
+        <v>8.5069444444444437E-3</v>
+      </c>
+      <c r="I85" s="1">
+        <v>46240.593865740739</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86">
+        <v>5777</v>
+      </c>
+      <c r="D86" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" t="s">
+        <v>10</v>
+      </c>
+      <c r="H86" s="2">
+        <v>6.4583333333333333E-3</v>
+      </c>
+      <c r="I86" s="1">
+        <v>46240.594560185185</v>
+      </c>
+      <c r="J86" s="2">
+        <v>0</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H87" s="2"/>
       <c r="I87" s="1"/>
       <c r="J87" s="2"/>
       <c r="K87" s="1"/>
     </row>
-    <row r="88" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H88" s="2"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H89" s="2"/>
       <c r="I89" s="1"/>
       <c r="J89" s="2"/>
       <c r="K89" s="1"/>
     </row>
-    <row r="90" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H90" s="2"/>
       <c r="I90" s="1"/>
       <c r="J90" s="2"/>
       <c r="K90" s="1"/>
     </row>
-    <row r="91" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H91" s="2"/>
       <c r="I91" s="1"/>
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H93" s="2"/>
       <c r="I93" s="1"/>
       <c r="J93" s="2"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H94" s="2"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
       <c r="K94" s="1"/>
     </row>
-    <row r="95" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H95" s="2"/>
       <c r="I95" s="1"/>
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H96" s="2"/>
       <c r="I96" s="1"/>
       <c r="J96" s="2"/>
@@ -43819,6 +44317,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -43833,11 +44332,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -43848,10 +44349,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -43869,14 +44373,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -43887,14 +44394,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -43921,6 +44431,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -43929,6 +44440,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -43941,22 +44453,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -43975,6 +44492,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -43985,10 +44503,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -43997,10 +44517,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -44014,82 +44536,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -44103,6 +44640,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44113,6 +44651,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -44120,6 +44659,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -44128,86 +44668,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44224,26 +44777,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -44274,6 +44833,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -44283,10 +44843,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -44299,14 +44861,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -44315,14 +44880,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -44341,26 +44909,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -44379,6 +44953,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -44387,10 +44962,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -44399,6 +44976,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -44411,10 +44989,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -44423,6 +45003,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -44431,14 +45012,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -44447,14 +45031,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -44471,76 +45058,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -44554,31 +45150,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -44591,10 +45194,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -44603,10 +45208,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -44615,6 +45222,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -44629,10 +45237,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -44641,10 +45251,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -44658,6 +45270,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -44673,14 +45286,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -44698,14 +45314,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -44718,10 +45337,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -44730,14 +45351,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -44746,10 +45370,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -44758,14 +45384,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -44787,6 +45416,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -44795,39 +45425,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D167E30F-F611-47AC-AF70-63A12DD3075A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE97901A-DFF3-41B2-A8BF-59DE2529CBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="46">
   <si>
     <t>Company Name</t>
   </si>
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>20</v>
       </c>
@@ -737,7 +737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>20</v>
       </c>
@@ -832,7 +832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2"/>
@@ -1125,7 +1125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>20</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>20</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>20</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -1832,33 +1832,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54">
-        <v>5654</v>
-      </c>
-      <c r="D54" t="s">
-        <v>35</v>
-      </c>
-      <c r="F54" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54" t="s">
-        <v>10</v>
-      </c>
-      <c r="H54" s="2">
-        <v>6.851851851851852E-3</v>
-      </c>
-      <c r="I54" s="1">
-        <v>46210.760995370372</v>
-      </c>
-      <c r="J54" s="2">
-        <v>1</v>
-      </c>
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" s="2"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="2"/>
       <c r="K54" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
@@ -1866,25 +1845,25 @@
         <v>20</v>
       </c>
       <c r="C55">
-        <v>5510</v>
+        <v>5654</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2">
-        <v>0</v>
+        <v>6.851851851851852E-3</v>
       </c>
       <c r="I55" s="1">
         <v>46210.760995370372</v>
       </c>
       <c r="J55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>11</v>
@@ -1895,25 +1874,25 @@
         <v>20</v>
       </c>
       <c r="C56">
-        <v>5511</v>
+        <v>5510</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H56" s="2">
-        <v>5.7754629629629631E-3</v>
+        <v>0</v>
       </c>
       <c r="I56" s="1">
-        <v>46210.761689814812</v>
+        <v>46210.760995370372</v>
       </c>
       <c r="J56" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>11</v>
@@ -1924,25 +1903,25 @@
         <v>20</v>
       </c>
       <c r="C57">
-        <v>5515</v>
+        <v>5511</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H57" s="2">
+        <v>5.7754629629629631E-3</v>
+      </c>
+      <c r="I57" s="1">
+        <v>46210.761689814812</v>
+      </c>
+      <c r="J57" s="2">
         <v>0</v>
-      </c>
-      <c r="I57" s="1">
-        <v>46210.762384259258</v>
-      </c>
-      <c r="J57" s="2">
-        <v>2</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>11</v>
@@ -1953,22 +1932,22 @@
         <v>20</v>
       </c>
       <c r="C58">
-        <v>5517</v>
+        <v>5515</v>
       </c>
       <c r="D58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2">
-        <v>8.6805555555555551E-4</v>
+        <v>0</v>
       </c>
       <c r="I58" s="1">
-        <v>46210.763078703705</v>
+        <v>46210.762384259258</v>
       </c>
       <c r="J58" s="2">
         <v>2</v>
@@ -1982,10 +1961,10 @@
         <v>20</v>
       </c>
       <c r="C59">
-        <v>5518</v>
+        <v>5517</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -1994,13 +1973,13 @@
         <v>10</v>
       </c>
       <c r="H59" s="2">
-        <v>6.1921296296296299E-3</v>
+        <v>8.6805555555555551E-4</v>
       </c>
       <c r="I59" s="1">
-        <v>46210.763773148145</v>
+        <v>46210.763078703705</v>
       </c>
       <c r="J59" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>11</v>
@@ -2011,10 +1990,10 @@
         <v>20</v>
       </c>
       <c r="C60">
-        <v>5519</v>
+        <v>5518</v>
       </c>
       <c r="D60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -2023,13 +2002,13 @@
         <v>10</v>
       </c>
       <c r="H60" s="2">
-        <v>1.0833333333333334E-2</v>
+        <v>6.1921296296296299E-3</v>
       </c>
       <c r="I60" s="1">
         <v>46210.763773148145</v>
       </c>
       <c r="J60" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>11</v>
@@ -2040,10 +2019,10 @@
         <v>20</v>
       </c>
       <c r="C61">
-        <v>5777</v>
+        <v>5519</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -2052,13 +2031,13 @@
         <v>10</v>
       </c>
       <c r="H61" s="2">
-        <v>6.0185185185185185E-3</v>
+        <v>1.0833333333333334E-2</v>
       </c>
       <c r="I61" s="1">
-        <v>46210.764467592591</v>
+        <v>46210.763773148145</v>
       </c>
       <c r="J61" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>11</v>
@@ -2069,22 +2048,22 @@
         <v>20</v>
       </c>
       <c r="C62">
-        <v>5493</v>
+        <v>5777</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H62" s="2">
-        <v>8.1018518518518516E-5</v>
+        <v>6.0185185185185185E-3</v>
       </c>
       <c r="I62" s="1">
-        <v>46240.584837962961</v>
+        <v>46210.764467592591</v>
       </c>
       <c r="J62" s="2">
         <v>0</v>
@@ -2094,40 +2073,40 @@
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H63" s="2"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="2"/>
+      <c r="B63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63">
+        <v>5493</v>
+      </c>
+      <c r="D63" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="2">
+        <v>7.0231481481481478E-2</v>
+      </c>
+      <c r="I63" s="1">
+        <v>46240.584837962961</v>
+      </c>
+      <c r="J63" s="2">
+        <v>3</v>
+      </c>
       <c r="K63" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H64" s="2"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64">
-        <v>5494</v>
-      </c>
-      <c r="D64" t="s">
-        <v>24</v>
-      </c>
-      <c r="F64" t="s">
-        <v>17</v>
-      </c>
-      <c r="G64" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" s="2">
-        <v>0</v>
-      </c>
-      <c r="I64" s="1">
-        <v>46240.584837962961</v>
-      </c>
-      <c r="J64" s="2">
-        <v>0</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
@@ -2135,10 +2114,10 @@
         <v>20</v>
       </c>
       <c r="C65">
-        <v>5497</v>
+        <v>5494</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F65" t="s">
         <v>17</v>
@@ -2150,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>46240.585532407407</v>
+        <v>46240.584837962961</v>
       </c>
       <c r="J65" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>11</v>
@@ -2164,10 +2143,10 @@
         <v>20</v>
       </c>
       <c r="C66">
-        <v>5499</v>
+        <v>5497</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F66" t="s">
         <v>17</v>
@@ -2176,13 +2155,13 @@
         <v>12</v>
       </c>
       <c r="H66" s="2">
-        <v>1.9675925925925926E-4</v>
+        <v>8.6805555555555551E-4</v>
       </c>
       <c r="I66" s="1">
-        <v>46240.586226851854</v>
+        <v>46240.585532407407</v>
       </c>
       <c r="J66" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>11</v>
@@ -2201,25 +2180,25 @@
         <v>20</v>
       </c>
       <c r="C68">
-        <v>5500</v>
+        <v>5499</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H68" s="2">
-        <v>0</v>
+        <v>8.6342592592592599E-3</v>
       </c>
       <c r="I68" s="1">
         <v>46240.586226851854</v>
       </c>
       <c r="J68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>11</v>
@@ -2230,10 +2209,10 @@
         <v>20</v>
       </c>
       <c r="C69">
-        <v>5501</v>
+        <v>5500</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
@@ -2245,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="I69" s="1">
-        <v>46240.586921296293</v>
+        <v>46240.586226851854</v>
       </c>
       <c r="J69" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>11</v>
@@ -2259,25 +2238,25 @@
         <v>20</v>
       </c>
       <c r="C70">
-        <v>5503</v>
+        <v>5501</v>
       </c>
       <c r="D70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F70" t="s">
         <v>17</v>
       </c>
       <c r="G70" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H70" s="2">
-        <v>8.6342592592592599E-3</v>
+        <v>0</v>
       </c>
       <c r="I70" s="1">
-        <v>46240.58761574074</v>
+        <v>46240.586921296293</v>
       </c>
       <c r="J70" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>11</v>
@@ -2288,22 +2267,22 @@
         <v>20</v>
       </c>
       <c r="C71">
-        <v>5505</v>
+        <v>5503</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F71" t="s">
         <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H71" s="2">
-        <v>1.1111111111111111E-3</v>
+        <v>8.6342592592592599E-3</v>
       </c>
       <c r="I71" s="1">
-        <v>46240.588310185187</v>
+        <v>46240.58761574074</v>
       </c>
       <c r="J71" s="2">
         <v>0</v>
@@ -2313,60 +2292,60 @@
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H72" s="2"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="2"/>
+      <c r="B72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72">
+        <v>5505</v>
+      </c>
+      <c r="D72" t="s">
+        <v>30</v>
+      </c>
+      <c r="F72" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72" s="2">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="I72" s="1">
+        <v>46240.588310185187</v>
+      </c>
+      <c r="J72" s="2">
+        <v>3</v>
+      </c>
       <c r="K72" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H73" s="2"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73">
-        <v>5507</v>
-      </c>
-      <c r="D73" t="s">
-        <v>32</v>
-      </c>
-      <c r="F73" t="s">
-        <v>17</v>
-      </c>
-      <c r="G73" t="s">
-        <v>10</v>
-      </c>
-      <c r="H73" s="2">
-        <v>9.0393518518518522E-3</v>
-      </c>
-      <c r="I73" s="1">
-        <v>46240.589004629626</v>
-      </c>
-      <c r="J73" s="2">
-        <v>0</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>20</v>
       </c>
       <c r="C74">
-        <v>5508</v>
+        <v>5507</v>
       </c>
       <c r="D74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F74" t="s">
         <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H74" s="2">
-        <v>0</v>
+        <v>9.0393518518518522E-3</v>
       </c>
       <c r="I74" s="1">
         <v>46240.589004629626</v>
@@ -2383,65 +2362,65 @@
         <v>20</v>
       </c>
       <c r="C75">
-        <v>5509</v>
+        <v>5508</v>
       </c>
       <c r="D75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F75" t="s">
         <v>17</v>
       </c>
       <c r="G75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H75" s="2">
         <v>0</v>
       </c>
       <c r="I75" s="1">
-        <v>46240.589699074073</v>
+        <v>46240.589004629626</v>
       </c>
       <c r="J75" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
+      <c r="H76" s="2"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
         <v>20</v>
       </c>
-      <c r="C76">
-        <v>5942</v>
-      </c>
-      <c r="D76" t="s">
-        <v>43</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="C77">
+        <v>5509</v>
+      </c>
+      <c r="D77" t="s">
+        <v>34</v>
+      </c>
+      <c r="F77" t="s">
         <v>17</v>
       </c>
-      <c r="G76" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" s="2">
+      <c r="G77" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="2">
         <v>0</v>
       </c>
-      <c r="I76" s="1">
-        <v>46240.59039351852</v>
-      </c>
-      <c r="J76" s="2">
-        <v>0</v>
-      </c>
-      <c r="K76" s="1" t="s">
+      <c r="I77" s="1">
+        <v>46240.589699074073</v>
+      </c>
+      <c r="J77" s="2">
+        <v>3</v>
+      </c>
+      <c r="K77" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H77" s="2"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
@@ -2449,57 +2428,36 @@
         <v>20</v>
       </c>
       <c r="C78">
-        <v>5654</v>
+        <v>5942</v>
       </c>
       <c r="D78" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F78" t="s">
         <v>17</v>
       </c>
       <c r="G78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H78" s="2">
-        <v>0</v>
+        <v>3.3564814814814812E-4</v>
       </c>
       <c r="I78" s="1">
         <v>46240.59039351852</v>
       </c>
       <c r="J78" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79">
-        <v>6025</v>
-      </c>
-      <c r="D79" t="s">
-        <v>44</v>
-      </c>
-      <c r="F79" t="s">
-        <v>17</v>
-      </c>
-      <c r="G79" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="2">
-        <v>0</v>
-      </c>
-      <c r="I79" s="1">
-        <v>46240.591087962966</v>
-      </c>
-      <c r="J79" s="2">
-        <v>0</v>
-      </c>
+      <c r="H79" s="2"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="2"/>
       <c r="K79" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
@@ -2507,22 +2465,22 @@
         <v>20</v>
       </c>
       <c r="C80">
-        <v>5511</v>
+        <v>5654</v>
       </c>
       <c r="D80" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H80" s="2">
-        <v>0</v>
+        <v>0.10100694444444444</v>
       </c>
       <c r="I80" s="1">
-        <v>46240.591782407406</v>
+        <v>46240.59039351852</v>
       </c>
       <c r="J80" s="2">
         <v>0</v>
@@ -2536,10 +2494,10 @@
         <v>20</v>
       </c>
       <c r="C81">
-        <v>5515</v>
+        <v>6025</v>
       </c>
       <c r="D81" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
@@ -2551,24 +2509,24 @@
         <v>0</v>
       </c>
       <c r="I81" s="1">
-        <v>46240.592476851853</v>
+        <v>46240.591087962966</v>
       </c>
       <c r="J81" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K81" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>20</v>
       </c>
       <c r="C82">
-        <v>6026</v>
+        <v>5511</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F82" t="s">
         <v>17</v>
@@ -2577,13 +2535,13 @@
         <v>10</v>
       </c>
       <c r="H82" s="2">
-        <v>7.3726851851851852E-3</v>
+        <v>6.898148148148148E-3</v>
       </c>
       <c r="I82" s="1">
-        <v>46240.592476851853</v>
+        <v>46240.591782407406</v>
       </c>
       <c r="J82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" s="1" t="s">
         <v>11</v>
@@ -2594,57 +2552,36 @@
         <v>20</v>
       </c>
       <c r="C83">
-        <v>5517</v>
+        <v>5515</v>
       </c>
       <c r="D83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F83" t="s">
         <v>17</v>
       </c>
       <c r="G83" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H83" s="2">
-        <v>6.9907407407407409E-3</v>
+        <v>5.7870370370370373E-5</v>
       </c>
       <c r="I83" s="1">
-        <v>46240.593171296299</v>
+        <v>46240.592476851853</v>
       </c>
       <c r="J83" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K83" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84">
-        <v>5518</v>
-      </c>
-      <c r="D84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F84" t="s">
-        <v>17</v>
-      </c>
-      <c r="G84" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" s="2">
-        <v>0</v>
-      </c>
-      <c r="I84" s="1">
-        <v>46240.593865740739</v>
-      </c>
-      <c r="J84" s="2">
-        <v>0</v>
-      </c>
+      <c r="H84" s="2"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="2"/>
       <c r="K84" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
@@ -2652,10 +2589,10 @@
         <v>20</v>
       </c>
       <c r="C85">
-        <v>5519</v>
+        <v>6026</v>
       </c>
       <c r="D85" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F85" t="s">
         <v>17</v>
@@ -2664,10 +2601,10 @@
         <v>10</v>
       </c>
       <c r="H85" s="2">
-        <v>8.5069444444444437E-3</v>
+        <v>7.3726851851851852E-3</v>
       </c>
       <c r="I85" s="1">
-        <v>46240.593865740739</v>
+        <v>46240.592476851853</v>
       </c>
       <c r="J85" s="2">
         <v>0</v>
@@ -2681,10 +2618,10 @@
         <v>20</v>
       </c>
       <c r="C86">
-        <v>5777</v>
+        <v>5517</v>
       </c>
       <c r="D86" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
@@ -2693,10 +2630,10 @@
         <v>10</v>
       </c>
       <c r="H86" s="2">
-        <v>6.4583333333333333E-3</v>
+        <v>6.9907407407407409E-3</v>
       </c>
       <c r="I86" s="1">
-        <v>46240.594560185185</v>
+        <v>46240.593171296299</v>
       </c>
       <c r="J86" s="2">
         <v>0</v>
@@ -2706,28 +2643,99 @@
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H87" s="2"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="1"/>
+      <c r="B87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87">
+        <v>5518</v>
+      </c>
+      <c r="D87" t="s">
+        <v>40</v>
+      </c>
+      <c r="F87" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" t="s">
+        <v>12</v>
+      </c>
+      <c r="H87" s="2">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1">
+        <v>46240.593865740739</v>
+      </c>
+      <c r="J87" s="2">
+        <v>2</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H88" s="2"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
-      <c r="K88" s="1"/>
+      <c r="K88" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H89" s="2"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="1"/>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89">
+        <v>5519</v>
+      </c>
+      <c r="D89" t="s">
+        <v>41</v>
+      </c>
+      <c r="F89" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" t="s">
+        <v>10</v>
+      </c>
+      <c r="H89" s="2">
+        <v>8.5069444444444437E-3</v>
+      </c>
+      <c r="I89" s="1">
+        <v>46240.593865740739</v>
+      </c>
+      <c r="J89" s="2">
+        <v>0</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H90" s="2"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="1"/>
+      <c r="B90" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90">
+        <v>5777</v>
+      </c>
+      <c r="D90" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" t="s">
+        <v>10</v>
+      </c>
+      <c r="H90" s="2">
+        <v>6.4583333333333333E-3</v>
+      </c>
+      <c r="I90" s="1">
+        <v>46240.594560185185</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H91" s="2"/>
@@ -2735,7 +2743,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -2855,7 +2863,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -2873,7 +2881,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -2945,7 +2953,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -3227,7 +3235,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -3257,7 +3265,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -3317,7 +3325,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -3425,7 +3433,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -3617,7 +3625,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -4133,7 +4141,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -4199,7 +4207,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -4211,7 +4219,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -4307,7 +4315,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -4319,7 +4327,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -4415,7 +4423,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -4475,7 +4483,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -43428,6 +43436,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43720,6 +43729,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -44030,6 +44041,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -44154,6 +44166,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -44165,6 +44178,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -44313,6 +44327,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -44323,10 +44338,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -44360,15 +44377,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -44409,18 +44429,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44436,6 +44460,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -44445,10 +44470,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -44484,10 +44511,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -44513,6 +44542,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -44527,6 +44557,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44561,6 +44592,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -44570,6 +44602,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -44579,6 +44612,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -44593,15 +44627,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -44631,6 +44666,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44651,11 +44687,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -44664,6 +44702,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -44693,6 +44732,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -44702,10 +44742,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -44720,14 +44762,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -44747,10 +44792,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -44770,9 +44817,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -44807,18 +44857,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44833,12 +44887,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -44853,10 +44907,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -44876,6 +44932,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -44895,6 +44952,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44904,6 +44962,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -44949,6 +45008,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -44958,6 +45018,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -44972,6 +45033,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -44981,10 +45043,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -44999,6 +45063,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -45008,6 +45073,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -45027,6 +45093,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -45046,10 +45113,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -45059,6 +45128,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -45069,10 +45139,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -45087,18 +45159,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -45118,10 +45194,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -45141,6 +45219,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -45171,7 +45250,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -45186,10 +45264,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -45204,6 +45284,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -45218,11 +45299,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -45232,6 +45313,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -45247,6 +45329,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -45261,6 +45344,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -45281,6 +45365,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -45306,11 +45391,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -45329,15 +45416,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -45347,6 +45435,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -45366,6 +45455,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -45380,6 +45470,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -45399,10 +45490,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45412,6 +45505,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -45422,6 +45516,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -45458,7 +45553,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -45467,6 +45561,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -45480,10 +45575,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE97901A-DFF3-41B2-A8BF-59DE2529CBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C4333A0-28F8-4BAB-A637-2278866BF062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="46">
   <si>
     <t>Company Name</t>
   </si>
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>20</v>
       </c>
@@ -737,7 +737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>20</v>
       </c>
@@ -832,7 +832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2"/>
@@ -1125,7 +1125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>20</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>20</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>20</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
@@ -2305,10 +2305,10 @@
         <v>17</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H72" s="2">
-        <v>1.1111111111111111E-3</v>
+        <v>8.1018518518518514E-3</v>
       </c>
       <c r="I72" s="1">
         <v>46240.588310185187</v>
@@ -2321,77 +2321,98 @@
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="2"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="2"/>
+      <c r="B73" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73">
+        <v>5507</v>
+      </c>
+      <c r="D73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" s="2">
+        <v>9.0393518518518522E-3</v>
+      </c>
+      <c r="I73" s="1">
+        <v>46240.589004629626</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0</v>
+      </c>
       <c r="K73" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>20</v>
       </c>
       <c r="C74">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="D74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F74" t="s">
         <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H74" s="2">
-        <v>9.0393518518518522E-3</v>
+        <v>0</v>
       </c>
       <c r="I74" s="1">
         <v>46240.589004629626</v>
       </c>
       <c r="J74" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
+      <c r="H75" s="2"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
         <v>20</v>
       </c>
-      <c r="C75">
-        <v>5508</v>
-      </c>
-      <c r="D75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="C76">
+        <v>5509</v>
+      </c>
+      <c r="D76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" t="s">
         <v>17</v>
       </c>
-      <c r="G75" t="s">
-        <v>12</v>
-      </c>
-      <c r="H75" s="2">
+      <c r="G76" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="2">
         <v>0</v>
       </c>
-      <c r="I75" s="1">
-        <v>46240.589004629626</v>
-      </c>
-      <c r="J75" s="2">
+      <c r="I76" s="1">
+        <v>46240.589699074073</v>
+      </c>
+      <c r="J76" s="2">
         <v>3</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H76" s="2"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
@@ -2399,22 +2420,22 @@
         <v>20</v>
       </c>
       <c r="C77">
-        <v>5509</v>
+        <v>5942</v>
       </c>
       <c r="D77" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F77" t="s">
         <v>17</v>
       </c>
       <c r="G77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H77" s="2">
-        <v>0</v>
+        <v>3.3564814814814812E-4</v>
       </c>
       <c r="I77" s="1">
-        <v>46240.589699074073</v>
+        <v>46240.59039351852</v>
       </c>
       <c r="J77" s="2">
         <v>3</v>
@@ -2424,40 +2445,40 @@
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
+      <c r="H78" s="2"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>20</v>
       </c>
-      <c r="C78">
-        <v>5942</v>
-      </c>
-      <c r="D78" t="s">
-        <v>43</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="C79">
+        <v>5654</v>
+      </c>
+      <c r="D79" t="s">
+        <v>35</v>
+      </c>
+      <c r="F79" t="s">
         <v>17</v>
       </c>
-      <c r="G78" t="s">
-        <v>12</v>
-      </c>
-      <c r="H78" s="2">
-        <v>3.3564814814814812E-4</v>
-      </c>
-      <c r="I78" s="1">
+      <c r="G79" t="s">
+        <v>10</v>
+      </c>
+      <c r="H79" s="2">
+        <v>0.10100694444444444</v>
+      </c>
+      <c r="I79" s="1">
         <v>46240.59039351852</v>
       </c>
-      <c r="J78" s="2">
-        <v>3</v>
-      </c>
-      <c r="K78" s="1" t="s">
+      <c r="J79" s="2">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H79" s="2"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
@@ -2465,25 +2486,25 @@
         <v>20</v>
       </c>
       <c r="C80">
-        <v>5654</v>
+        <v>6025</v>
       </c>
       <c r="D80" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H80" s="2">
-        <v>0.10100694444444444</v>
+        <v>0</v>
       </c>
       <c r="I80" s="1">
-        <v>46240.59039351852</v>
+        <v>46240.591087962966</v>
       </c>
       <c r="J80" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K80" s="1" t="s">
         <v>11</v>
@@ -2494,94 +2515,94 @@
         <v>20</v>
       </c>
       <c r="C81">
-        <v>6025</v>
+        <v>5511</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
       </c>
       <c r="G81" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H81" s="2">
-        <v>0</v>
+        <v>6.898148148148148E-3</v>
       </c>
       <c r="I81" s="1">
-        <v>46240.591087962966</v>
+        <v>46240.591782407406</v>
       </c>
       <c r="J81" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>20</v>
       </c>
       <c r="C82">
-        <v>5511</v>
+        <v>5515</v>
       </c>
       <c r="D82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F82" t="s">
         <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H82" s="2">
-        <v>6.898148148148148E-3</v>
+        <v>6.134259259259259E-4</v>
       </c>
       <c r="I82" s="1">
-        <v>46240.591782407406</v>
+        <v>46240.592476851853</v>
       </c>
       <c r="J82" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K82" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
+      <c r="H83" s="2"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
         <v>20</v>
       </c>
-      <c r="C83">
-        <v>5515</v>
-      </c>
-      <c r="D83" t="s">
-        <v>38</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="C84">
+        <v>6026</v>
+      </c>
+      <c r="D84" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84" t="s">
         <v>17</v>
       </c>
-      <c r="G83" t="s">
-        <v>12</v>
-      </c>
-      <c r="H83" s="2">
-        <v>5.7870370370370373E-5</v>
-      </c>
-      <c r="I83" s="1">
+      <c r="G84" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" s="2">
+        <v>7.3726851851851852E-3</v>
+      </c>
+      <c r="I84" s="1">
         <v>46240.592476851853</v>
       </c>
-      <c r="J83" s="2">
-        <v>3</v>
-      </c>
-      <c r="K83" s="1" t="s">
+      <c r="J84" s="2">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H84" s="2"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
@@ -2589,10 +2610,10 @@
         <v>20</v>
       </c>
       <c r="C85">
-        <v>6026</v>
+        <v>5517</v>
       </c>
       <c r="D85" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F85" t="s">
         <v>17</v>
@@ -2601,10 +2622,10 @@
         <v>10</v>
       </c>
       <c r="H85" s="2">
-        <v>7.3726851851851852E-3</v>
+        <v>6.9907407407407409E-3</v>
       </c>
       <c r="I85" s="1">
-        <v>46240.592476851853</v>
+        <v>46240.593171296299</v>
       </c>
       <c r="J85" s="2">
         <v>0</v>
@@ -2618,65 +2639,65 @@
         <v>20</v>
       </c>
       <c r="C86">
-        <v>5517</v>
+        <v>5518</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
       </c>
       <c r="G86" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H86" s="2">
-        <v>6.9907407407407409E-3</v>
+        <v>0</v>
       </c>
       <c r="I86" s="1">
-        <v>46240.593171296299</v>
+        <v>46240.593865740739</v>
       </c>
       <c r="J86" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
+      <c r="H87" s="2"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
         <v>20</v>
       </c>
-      <c r="C87">
-        <v>5518</v>
-      </c>
-      <c r="D87" t="s">
-        <v>40</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="C88">
+        <v>5519</v>
+      </c>
+      <c r="D88" t="s">
+        <v>41</v>
+      </c>
+      <c r="F88" t="s">
         <v>17</v>
       </c>
-      <c r="G87" t="s">
-        <v>12</v>
-      </c>
-      <c r="H87" s="2">
+      <c r="G88" t="s">
+        <v>10</v>
+      </c>
+      <c r="H88" s="2">
+        <v>8.5069444444444437E-3</v>
+      </c>
+      <c r="I88" s="1">
+        <v>46240.593865740739</v>
+      </c>
+      <c r="J88" s="2">
         <v>0</v>
       </c>
-      <c r="I87" s="1">
-        <v>46240.593865740739</v>
-      </c>
-      <c r="J87" s="2">
-        <v>2</v>
-      </c>
-      <c r="K87" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H88" s="2"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
@@ -2684,10 +2705,10 @@
         <v>20</v>
       </c>
       <c r="C89">
-        <v>5519</v>
+        <v>5777</v>
       </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" t="s">
         <v>17</v>
@@ -2696,10 +2717,10 @@
         <v>10</v>
       </c>
       <c r="H89" s="2">
-        <v>8.5069444444444437E-3</v>
+        <v>6.4583333333333333E-3</v>
       </c>
       <c r="I89" s="1">
-        <v>46240.593865740739</v>
+        <v>46240.594560185185</v>
       </c>
       <c r="J89" s="2">
         <v>0</v>
@@ -2709,33 +2730,10 @@
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>20</v>
-      </c>
-      <c r="C90">
-        <v>5777</v>
-      </c>
-      <c r="D90" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" t="s">
-        <v>17</v>
-      </c>
-      <c r="G90" t="s">
-        <v>10</v>
-      </c>
-      <c r="H90" s="2">
-        <v>6.4583333333333333E-3</v>
-      </c>
-      <c r="I90" s="1">
-        <v>46240.594560185185</v>
-      </c>
-      <c r="J90" s="2">
-        <v>0</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H90" s="2"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="1"/>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H91" s="2"/>
@@ -2743,7 +2741,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
@@ -2863,7 +2861,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -2881,7 +2879,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="1"/>
       <c r="J115" s="2"/>
@@ -2953,7 +2951,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="1"/>
       <c r="J127" s="2"/>
@@ -3235,7 +3233,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -3265,7 +3263,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -3325,7 +3323,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -3433,7 +3431,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -3625,7 +3623,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -4141,7 +4139,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -4207,7 +4205,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -4219,7 +4217,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -4315,7 +4313,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -4327,7 +4325,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -4423,7 +4421,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -4483,7 +4481,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -43436,7 +43434,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43729,8 +43726,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -44041,7 +44036,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -44166,7 +44160,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -44178,7 +44171,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -44327,35 +44319,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -44366,44 +44352,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -44414,37 +44391,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44455,52 +44425,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -44511,17 +44471,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44532,32 +44489,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44567,106 +44518,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44676,7 +44607,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44687,127 +44617,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44817,62 +44721,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44892,67 +44783,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44962,38 +44840,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -45008,117 +44879,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -45127,99 +44975,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -45229,23 +45058,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -45254,52 +45079,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -45313,38 +45128,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -45354,7 +45162,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -45365,23 +45172,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -45391,37 +45194,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -45430,72 +45226,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45505,76 +45287,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Express-Tow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C4333A0-28F8-4BAB-A637-2278866BF062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A811C1E-9586-4B37-881E-B77B259EB1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -43434,6 +43434,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -43726,6 +43727,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -44036,6 +44039,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -44160,6 +44164,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -44171,6 +44176,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -44319,29 +44325,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -44352,35 +44364,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -44391,30 +44412,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -44425,42 +44453,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -44471,14 +44509,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -44489,26 +44530,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -44518,86 +44565,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -44607,6 +44675,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -44617,101 +44686,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -44721,49 +44816,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -44778,59 +44886,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -44840,31 +44962,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -44874,99 +45003,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -44975,80 +45128,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -45058,67 +45230,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -45128,31 +45316,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -45162,6 +45357,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -45172,19 +45368,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -45194,90 +45394,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -45287,51 +45509,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
